--- a/api/_lib/CAMPAIGN-TEMPLATE.xlsx
+++ b/api/_lib/CAMPAIGN-TEMPLATE.xlsx
@@ -1296,7 +1296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC14"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1366,7 +1366,7 @@
           <t>bid_amount_minor</t>
         </is>
       </c>
-      <c r="H1" s="17" t="inlineStr">
+      <c r="H1" s="18" t="inlineStr">
         <is>
           <t>countries</t>
         </is>
@@ -1563,7 +1563,7 @@
     <row r="3">
       <c r="A3" s="19" t="inlineStr">
         <is>
-          <t>Q3 UK Retarget 30d</t>
+          <t>Q3 Spanish speakers WW</t>
         </is>
       </c>
       <c r="B3" s="19" t="inlineStr"/>
@@ -1580,26 +1580,14 @@
       </c>
       <c r="F3" s="19" t="inlineStr"/>
       <c r="G3" s="19" t="inlineStr"/>
-      <c r="H3" s="19" t="inlineStr">
-        <is>
-          <t>GB,IE</t>
-        </is>
-      </c>
+      <c r="H3" s="19" t="inlineStr"/>
       <c r="I3" s="19" t="inlineStr"/>
-      <c r="J3" s="19" t="inlineStr">
-        <is>
-          <t>London</t>
-        </is>
-      </c>
+      <c r="J3" s="19" t="inlineStr"/>
       <c r="K3" s="19" t="inlineStr"/>
-      <c r="L3" s="19" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
+      <c r="L3" s="19" t="inlineStr"/>
       <c r="M3" s="19" t="inlineStr">
         <is>
-          <t>English (UK),English (US)</t>
+          <t>Spanish</t>
         </is>
       </c>
       <c r="N3" s="19" t="inlineStr">
@@ -1615,16 +1603,8 @@
       </c>
       <c r="Q3" s="19" t="inlineStr"/>
       <c r="R3" s="19" t="inlineStr"/>
-      <c r="S3" s="19" t="inlineStr">
-        <is>
-          <t>Website visitors 30d</t>
-        </is>
-      </c>
-      <c r="T3" s="19" t="inlineStr">
-        <is>
-          <t>Purchasers 180d</t>
-        </is>
-      </c>
+      <c r="S3" s="19" t="inlineStr"/>
+      <c r="T3" s="19" t="inlineStr"/>
       <c r="U3" s="19" t="inlineStr">
         <is>
           <t>no</t>
@@ -1673,61 +1653,68 @@
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
         <is>
-          <t>countries / excluded_countries: ISO codes, comma separated. See the Countries tab. e.g. GB,IE</t>
+          <t>countries: ISO codes comma separated (GB,IE), or 'worldwide'. See the Countries tab.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="20" t="inlineStr">
         <is>
-          <t>cities / regions: names, comma separated. e.g. London,Manchester  (Claude resolves them to Meta IDs)</t>
+          <t xml:space="preserve">   Targeting a LANGUAGE only? Leave countries blank and fill languages -&gt; worldwide in that language.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>location_types: home+recent (default), home, recent, travel_in</t>
+          <t>cities / regions: names, comma separated. e.g. London,Manchester  (Claude resolves them to Meta IDs)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="20" t="inlineStr">
         <is>
-          <t>languages: names EXACTLY as on the Languages tab, comma separated. Blank = all languages.</t>
+          <t>location_types: home+recent (default), home, recent, travel_in</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>genders: All / Men / Women.   advantage_audience: yes lets Meta expand beyond your targeting.</t>
+          <t>languages: names EXACTLY as on the Languages tab, comma separated. Blank = all languages.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="20" t="inlineStr">
         <is>
-          <t>interests / custom_audiences: names, comma separated. Claude resolves and CONFIRMS each one before building.</t>
+          <t>genders: All / Men / Women.   advantage_audience: yes lets Meta expand beyond your targeting.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>publisher_platforms / positions: blank = Advantage+ placements (all). Fill only to restrict.</t>
+          <t>interests / custom_audiences: names, comma separated. Claude resolves and CONFIRMS each one before building.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="20" t="inlineStr">
         <is>
-          <t>budgets: fill daily OR lifetime, never both. Leave BOTH blank if the campaign is CBO.</t>
+          <t>publisher_platforms / positions: blank = Advantage+ placements (all). Fill only to restrict.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>budgets: fill daily OR lifetime, never both. Leave BOTH blank if the campaign is CBO.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>start_time / end_time: 2026-09-01T00:00:00+0300</t>
         </is>
@@ -1770,7 +1757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1867,12 +1854,12 @@
       </c>
       <c r="D2" s="21" t="inlineStr">
         <is>
-          <t>Three months of clear skin, or your money back. Over 12,000 five star reviews.</t>
+          <t>Three months of clear skin, or your money back. | Over 12,000 five star reviews. | Results by week six, or you pay nothing.</t>
         </is>
       </c>
       <c r="E2" s="21" t="inlineStr">
         <is>
-          <t>Clinically proven</t>
+          <t>Clinically proven | Dermatologist tested | 90-day guarantee</t>
         </is>
       </c>
       <c r="F2" s="21" t="inlineStr">
@@ -2012,6 +1999,27 @@
       <c r="A9" s="20" t="inlineStr">
         <is>
           <t>cta / link / url_tags / page_id / instagram_user_id: blank inherits the Campaign tab default.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>SEVERAL PRIMARY TEXTS OR HEADLINES IN ONE AD: separate them with |   Hook one | Hook two | Hook three</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Meta rotates them within the single ad and learns which wins. Max 5 texts and 5 headlines.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Row 2 above shows it. Commas are NOT separators - ad copy is full of commas.</t>
         </is>
       </c>
     </row>
